--- a/03_Outputs/all/03_DS/ds_idx12_salud.xlsx
+++ b/03_Outputs/all/03_DS/ds_idx12_salud.xlsx
@@ -398,7 +398,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.649182479416691</v>
+        <v>0.649182479416692</v>
       </c>
       <c r="D2">
         <v>1.903343619801947</v>
@@ -407,7 +407,7 @@
         <v>1.318407379495635</v>
       </c>
       <c r="F2">
-        <v>0.04990520758779628</v>
+        <v>0.04990520758779698</v>
       </c>
     </row>
     <row r="3">
@@ -422,16 +422,16 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.6552944776682293</v>
+        <v>0.655294477668229</v>
       </c>
       <c r="D3">
-        <v>-0.2547918202400273</v>
+        <v>-0.2547918202400271</v>
       </c>
       <c r="E3">
-        <v>-0.5600225697331443</v>
+        <v>-0.5600225697331446</v>
       </c>
       <c r="F3">
-        <v>-0.1230005968737573</v>
+        <v>-0.1230005968737565</v>
       </c>
     </row>
     <row r="4">
@@ -446,16 +446,16 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.7226875583570224</v>
+        <v>0.7226875583570227</v>
       </c>
       <c r="D4">
-        <v>0.9487337377900397</v>
+        <v>0.9487337377900399</v>
       </c>
       <c r="E4">
-        <v>0.3985919904536341</v>
+        <v>0.3985919904536339</v>
       </c>
       <c r="F4">
-        <v>-0.05284132657832347</v>
+        <v>-0.05284132657832263</v>
       </c>
     </row>
     <row r="5">
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.6708883399990826</v>
+        <v>0.6708883399990824</v>
       </c>
       <c r="D5">
-        <v>-0.1078589953642939</v>
+        <v>-0.1078589953642936</v>
       </c>
       <c r="E5">
         <v>-0.4763024125897913</v>
       </c>
       <c r="F5">
-        <v>-0.1112244724266597</v>
+        <v>-0.1112244724266588</v>
       </c>
     </row>
     <row r="6">
@@ -494,16 +494,16 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.6121543735732122</v>
+        <v>0.6121543735732117</v>
       </c>
       <c r="D6">
-        <v>-0.376724482484062</v>
+        <v>-0.3767244824840616</v>
       </c>
       <c r="E6">
-        <v>-0.7083702276567904</v>
+        <v>-0.7083702276567905</v>
       </c>
       <c r="F6">
-        <v>-0.08166865199302195</v>
+        <v>-0.08166865199302115</v>
       </c>
     </row>
     <row r="7">
@@ -521,13 +521,13 @@
         <v>0.2996810766373806</v>
       </c>
       <c r="D7">
-        <v>-0.7621859434949806</v>
+        <v>-0.7621859434949799</v>
       </c>
       <c r="E7">
-        <v>0.2171767087896554</v>
+        <v>0.2171767087896553</v>
       </c>
       <c r="F7">
-        <v>-0.2258138206011666</v>
+        <v>-0.2258138206011658</v>
       </c>
     </row>
     <row r="8">
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.6601703485092254</v>
+        <v>0.660170348509225</v>
       </c>
       <c r="D8">
-        <v>-0.2307322948136941</v>
+        <v>-0.2307322948136939</v>
       </c>
       <c r="E8">
-        <v>-0.5690578981878271</v>
+        <v>-0.5690578981878274</v>
       </c>
       <c r="F8">
-        <v>-0.1214931483446492</v>
+        <v>-0.1214931483446484</v>
       </c>
     </row>
     <row r="9">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.7023666238237822</v>
+        <v>0.7023666238237823</v>
       </c>
       <c r="D9">
-        <v>0.5342303448940463</v>
+        <v>0.5342303448940465</v>
       </c>
       <c r="E9">
-        <v>0.05536920734346143</v>
+        <v>0.05536920734346113</v>
       </c>
       <c r="F9">
-        <v>-0.07574514872541573</v>
+        <v>-0.07574514872541493</v>
       </c>
     </row>
     <row r="10">
@@ -590,16 +590,16 @@
         </is>
       </c>
       <c r="C10">
-        <v>0.6659286934822117</v>
+        <v>0.6659286934822114</v>
       </c>
       <c r="D10">
-        <v>-0.2090251255658861</v>
+        <v>-0.2090251255658858</v>
       </c>
       <c r="E10">
-        <v>-0.5600713789224482</v>
+        <v>-0.5600713789224484</v>
       </c>
       <c r="F10">
-        <v>-0.1168145136498645</v>
+        <v>-0.1168145136498636</v>
       </c>
     </row>
     <row r="11">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="C11">
-        <v>-1.518105063345946</v>
+        <v>-1.518105063345943</v>
       </c>
       <c r="D11">
-        <v>-3.359569983273734</v>
+        <v>-3.359569983273731</v>
       </c>
       <c r="E11">
         <v>2.993149512853571</v>
@@ -638,16 +638,16 @@
         </is>
       </c>
       <c r="C12">
-        <v>0.02243721391260747</v>
+        <v>0.02243721391260872</v>
       </c>
       <c r="D12">
         <v>1.10350370719257</v>
       </c>
       <c r="E12">
-        <v>2.110758594586655</v>
+        <v>2.110758594586654</v>
       </c>
       <c r="F12">
-        <v>0.06218961332126093</v>
+        <v>0.06218961332126136</v>
       </c>
     </row>
     <row r="13">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="C13">
-        <v>0.1545079694714379</v>
+        <v>0.1545079694714382</v>
       </c>
       <c r="D13">
-        <v>-1.010947569075622</v>
+        <v>-1.010947569075621</v>
       </c>
       <c r="E13">
-        <v>0.5201998784699567</v>
+        <v>0.5201998784699565</v>
       </c>
       <c r="F13">
-        <v>-0.2458412564355969</v>
+        <v>-0.2458412564355962</v>
       </c>
     </row>
     <row r="14">
@@ -692,10 +692,10 @@
         <v>1.475068385162126</v>
       </c>
       <c r="E14">
-        <v>1.104596704250918</v>
+        <v>1.104596704250919</v>
       </c>
       <c r="F14">
-        <v>1.041420260183706</v>
+        <v>1.041420260183705</v>
       </c>
     </row>
     <row r="15">
@@ -710,16 +710,16 @@
         </is>
       </c>
       <c r="C15">
-        <v>-0.1904003583695982</v>
+        <v>-0.1904003583695988</v>
       </c>
       <c r="D15">
-        <v>-0.6491308749880073</v>
+        <v>-0.6491308749880066</v>
       </c>
       <c r="E15">
-        <v>-0.404860261079705</v>
+        <v>-0.4048602610797045</v>
       </c>
       <c r="F15">
-        <v>0.178556420187728</v>
+        <v>0.1785564201877281</v>
       </c>
     </row>
     <row r="16">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C16">
-        <v>0.5645785307286488</v>
+        <v>0.5645785307286491</v>
       </c>
       <c r="D16">
-        <v>0.1135930847382063</v>
+        <v>0.1135930847382067</v>
       </c>
       <c r="E16">
-        <v>0.2369397242063655</v>
+        <v>0.2369397242063653</v>
       </c>
       <c r="F16">
-        <v>-0.1500575631783665</v>
+        <v>-0.1500575631783658</v>
       </c>
     </row>
     <row r="17">
@@ -758,16 +758,16 @@
         </is>
       </c>
       <c r="C17">
-        <v>0.6715190350221977</v>
+        <v>0.6715190350221976</v>
       </c>
       <c r="D17">
-        <v>0.01710848025490489</v>
+        <v>0.01710848025490522</v>
       </c>
       <c r="E17">
-        <v>-0.3762203168482964</v>
+        <v>-0.3762203168482965</v>
       </c>
       <c r="F17">
-        <v>-0.1100220442436866</v>
+        <v>-0.1100220442436858</v>
       </c>
     </row>
     <row r="18">
@@ -782,16 +782,16 @@
         </is>
       </c>
       <c r="C18">
-        <v>0.6893937191068138</v>
+        <v>0.6893937191068142</v>
       </c>
       <c r="D18">
-        <v>1.209965915507822</v>
+        <v>1.209965915507823</v>
       </c>
       <c r="E18">
-        <v>0.604942057182242</v>
+        <v>0.6049420571822416</v>
       </c>
       <c r="F18">
-        <v>0.004542878963516877</v>
+        <v>0.004542878963517655</v>
       </c>
     </row>
     <row r="19">
@@ -806,16 +806,16 @@
         </is>
       </c>
       <c r="C19">
-        <v>0.6718056307686224</v>
+        <v>0.6718056307686222</v>
       </c>
       <c r="D19">
-        <v>-0.08914823500903085</v>
+        <v>-0.08914823500903053</v>
       </c>
       <c r="E19">
-        <v>-0.4608092722360469</v>
+        <v>-0.460809272236047</v>
       </c>
       <c r="F19">
-        <v>-0.110190589629176</v>
+        <v>-0.1101905896291751</v>
       </c>
     </row>
     <row r="20">
@@ -830,16 +830,16 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.6457411233251041</v>
+        <v>0.6457411233251042</v>
       </c>
       <c r="D20">
-        <v>0.6584719829105846</v>
+        <v>0.658471982910585</v>
       </c>
       <c r="E20">
-        <v>0.2394474450303846</v>
+        <v>0.2394474450303843</v>
       </c>
       <c r="F20">
-        <v>-0.05388288265810377</v>
+        <v>-0.05388288265810304</v>
       </c>
     </row>
     <row r="21">
@@ -854,16 +854,16 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.5927213596489083</v>
+        <v>0.5927213596489079</v>
       </c>
       <c r="D21">
-        <v>-0.0659930004914013</v>
+        <v>-0.065993000491401</v>
       </c>
       <c r="E21">
-        <v>-0.4592791002157383</v>
+        <v>-0.4592791002157385</v>
       </c>
       <c r="F21">
-        <v>-0.03571212128259937</v>
+        <v>-0.0357121212825986</v>
       </c>
     </row>
     <row r="22">
@@ -878,16 +878,16 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.6480432855075305</v>
+        <v>0.6480432855075302</v>
       </c>
       <c r="D22">
-        <v>-0.1300317779179148</v>
+        <v>-0.1300317779179144</v>
       </c>
       <c r="E22">
-        <v>-0.4549348878661244</v>
+        <v>-0.4549348878661246</v>
       </c>
       <c r="F22">
-        <v>-0.1037563311774629</v>
+        <v>-0.1037563311774621</v>
       </c>
     </row>
     <row r="23">
@@ -902,16 +902,16 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.6476303485709668</v>
+        <v>0.6476303485709667</v>
       </c>
       <c r="D23">
-        <v>0.4033872418119298</v>
+        <v>0.4033872418119301</v>
       </c>
       <c r="E23">
-        <v>0.007732264578523099</v>
+        <v>0.007732264578522934</v>
       </c>
       <c r="F23">
-        <v>-0.07785529596882269</v>
+        <v>-0.07785529596882185</v>
       </c>
     </row>
     <row r="24">
@@ -926,16 +926,16 @@
         </is>
       </c>
       <c r="C24">
-        <v>0.4306397485292138</v>
+        <v>0.4306397485292141</v>
       </c>
       <c r="D24">
-        <v>0.1448874301946988</v>
+        <v>0.1448874301946992</v>
       </c>
       <c r="E24">
-        <v>0.5157576837814259</v>
+        <v>0.5157576837814257</v>
       </c>
       <c r="F24">
-        <v>-0.1033479820310598</v>
+        <v>-0.1033479820310591</v>
       </c>
     </row>
     <row r="25">
@@ -950,16 +950,16 @@
         </is>
       </c>
       <c r="C25">
-        <v>0.2005090766954865</v>
+        <v>0.2005090766954866</v>
       </c>
       <c r="D25">
-        <v>-0.7863328735477371</v>
+        <v>-0.7863328735477363</v>
       </c>
       <c r="E25">
-        <v>0.3598651189197296</v>
+        <v>0.3598651189197295</v>
       </c>
       <c r="F25">
-        <v>-0.1599069866320857</v>
+        <v>-0.1599069866320851</v>
       </c>
     </row>
     <row r="26">
@@ -977,13 +977,13 @@
         <v>-1.148856275870679</v>
       </c>
       <c r="D26">
-        <v>-0.2182381665989906</v>
+        <v>-0.21823816659899</v>
       </c>
       <c r="E26">
-        <v>-0.9402454998093757</v>
+        <v>-0.9402454998093741</v>
       </c>
       <c r="F26">
-        <v>-0.2771438775842607</v>
+        <v>-0.277143877584262</v>
       </c>
     </row>
     <row r="27">
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="C27">
-        <v>0.6612699394771899</v>
+        <v>0.6612699394771896</v>
       </c>
       <c r="D27">
-        <v>-0.249471439142872</v>
+        <v>-0.2494714391428717</v>
       </c>
       <c r="E27">
-        <v>-0.5952153907257571</v>
+        <v>-0.5952153907257572</v>
       </c>
       <c r="F27">
-        <v>-0.1218260749364823</v>
+        <v>-0.1218260749364815</v>
       </c>
     </row>
     <row r="28">
@@ -1022,16 +1022,16 @@
         </is>
       </c>
       <c r="C28">
-        <v>0.609341017183238</v>
+        <v>0.6093410171832377</v>
       </c>
       <c r="D28">
-        <v>0.08544843017743552</v>
+        <v>0.08544843017743588</v>
       </c>
       <c r="E28">
-        <v>-0.298427776623131</v>
+        <v>-0.2984277766231311</v>
       </c>
       <c r="F28">
-        <v>-0.03750647394093982</v>
+        <v>-0.03750647394093912</v>
       </c>
     </row>
     <row r="29">
@@ -1046,16 +1046,16 @@
         </is>
       </c>
       <c r="C29">
-        <v>0.1387480065714002</v>
+        <v>0.1387480065714009</v>
       </c>
       <c r="D29">
-        <v>-0.8894413952486926</v>
+        <v>-0.8894413952486919</v>
       </c>
       <c r="E29">
         <v>1.109783087645926</v>
       </c>
       <c r="F29">
-        <v>-0.3696557999093998</v>
+        <v>-0.3696557999093991</v>
       </c>
     </row>
     <row r="30">
@@ -1070,16 +1070,16 @@
         </is>
       </c>
       <c r="C30">
-        <v>0.6207539776043509</v>
+        <v>0.6207539776043507</v>
       </c>
       <c r="D30">
-        <v>0.2418292539145692</v>
+        <v>0.2418292539145696</v>
       </c>
       <c r="E30">
-        <v>-0.2019377935947967</v>
+        <v>-0.201937793594797</v>
       </c>
       <c r="F30">
-        <v>-0.03243488136893844</v>
+        <v>-0.03243488136893777</v>
       </c>
     </row>
     <row r="31">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="C31">
-        <v>0.4579066493045724</v>
+        <v>0.4579066493045721</v>
       </c>
       <c r="D31">
-        <v>-0.2024542471451821</v>
+        <v>-0.2024542471451817</v>
       </c>
       <c r="E31">
         <v>-0.3220268699120483</v>
       </c>
       <c r="F31">
-        <v>-0.03318973502059339</v>
+        <v>-0.03318973502059272</v>
       </c>
     </row>
     <row r="32">
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="C32">
-        <v>0.7075360160264023</v>
+        <v>0.7075360160264024</v>
       </c>
       <c r="D32">
-        <v>0.6396748363218931</v>
+        <v>0.6396748363218933</v>
       </c>
       <c r="E32">
-        <v>0.1426808010041275</v>
+        <v>0.142680801004127</v>
       </c>
       <c r="F32">
-        <v>-0.06991870214030906</v>
+        <v>-0.06991870214030821</v>
       </c>
     </row>
     <row r="33">
@@ -1142,16 +1142,16 @@
         </is>
       </c>
       <c r="C33">
-        <v>-1.386244293904753</v>
+        <v>-1.386244293904754</v>
       </c>
       <c r="D33">
-        <v>-0.1861037586252551</v>
+        <v>-0.1861037586252542</v>
       </c>
       <c r="E33">
-        <v>-0.02307645965165112</v>
+        <v>-0.02307645965165003</v>
       </c>
       <c r="F33">
-        <v>0.8782301024872499</v>
+        <v>0.8782301024872488</v>
       </c>
     </row>
     <row r="34">
@@ -1166,16 +1166,16 @@
         </is>
       </c>
       <c r="C34">
-        <v>0.7106219175637604</v>
+        <v>0.7106219175637607</v>
       </c>
       <c r="D34">
-        <v>0.7675304773534879</v>
+        <v>0.767530477353488</v>
       </c>
       <c r="E34">
-        <v>0.2479235114268174</v>
+        <v>0.2479235114268168</v>
       </c>
       <c r="F34">
-        <v>-0.05958841070049576</v>
+        <v>-0.05958841070049492</v>
       </c>
     </row>
     <row r="35">
@@ -1190,16 +1190,16 @@
         </is>
       </c>
       <c r="C35">
-        <v>0.6864163458494721</v>
+        <v>0.686416345849472</v>
       </c>
       <c r="D35">
-        <v>0.2088789528519586</v>
+        <v>0.2088789528519588</v>
       </c>
       <c r="E35">
-        <v>-0.2140327135558299</v>
+        <v>-0.2140327135558301</v>
       </c>
       <c r="F35">
-        <v>-0.09372278303759292</v>
+        <v>-0.09372278303759213</v>
       </c>
     </row>
     <row r="36">
@@ -1214,16 +1214,16 @@
         </is>
       </c>
       <c r="C36">
-        <v>-1.259974559302736</v>
+        <v>-1.259974559302735</v>
       </c>
       <c r="D36">
-        <v>0.9563679821454411</v>
+        <v>0.9563679821454417</v>
       </c>
       <c r="E36">
-        <v>1.963734154601114</v>
+        <v>1.963734154601115</v>
       </c>
       <c r="F36">
-        <v>0.1646871741755562</v>
+        <v>0.1646871741755552</v>
       </c>
     </row>
     <row r="37">
@@ -1238,16 +1238,16 @@
         </is>
       </c>
       <c r="C37">
-        <v>-1.935476614322985</v>
+        <v>-1.935476614322986</v>
       </c>
       <c r="D37">
-        <v>0.3488857595271605</v>
+        <v>0.3488857595271615</v>
       </c>
       <c r="E37">
-        <v>-0.2207875136956177</v>
+        <v>-0.2207875136956161</v>
       </c>
       <c r="F37">
-        <v>1.56582309197817</v>
+        <v>1.565823091978168</v>
       </c>
     </row>
     <row r="38">
@@ -1262,16 +1262,16 @@
         </is>
       </c>
       <c r="C38">
-        <v>-0.003345881052263974</v>
+        <v>-0.003345881052264549</v>
       </c>
       <c r="D38">
-        <v>0.0830094987497421</v>
+        <v>0.08300949874974263</v>
       </c>
       <c r="E38">
-        <v>-0.03799530037997127</v>
+        <v>-0.03799530037997107</v>
       </c>
       <c r="F38">
-        <v>0.4386310941377582</v>
+        <v>0.4386310941377584</v>
       </c>
     </row>
     <row r="39">
@@ -1286,16 +1286,16 @@
         </is>
       </c>
       <c r="C39">
-        <v>0.521241500976842</v>
+        <v>0.5212415009768415</v>
       </c>
       <c r="D39">
-        <v>-0.3183652538731884</v>
+        <v>-0.318365253873188</v>
       </c>
       <c r="E39">
         <v>-0.5635471343938301</v>
       </c>
       <c r="F39">
-        <v>-0.02023586086556492</v>
+        <v>-0.0202358608655642</v>
       </c>
     </row>
     <row r="40">
@@ -1313,13 +1313,13 @@
         <v>0.6881793820715968</v>
       </c>
       <c r="D40">
-        <v>0.2448411028541567</v>
+        <v>0.2448411028541571</v>
       </c>
       <c r="E40">
-        <v>-0.1842548409933318</v>
+        <v>-0.1842548409933321</v>
       </c>
       <c r="F40">
-        <v>-0.09173565651029798</v>
+        <v>-0.09173565651029714</v>
       </c>
     </row>
     <row r="41">
@@ -1334,16 +1334,16 @@
         </is>
       </c>
       <c r="C41">
-        <v>0.630092053370205</v>
+        <v>0.6300920533702046</v>
       </c>
       <c r="D41">
-        <v>-0.3068153855551908</v>
+        <v>-0.3068153855551905</v>
       </c>
       <c r="E41">
-        <v>-0.6292309240952229</v>
+        <v>-0.6292309240952231</v>
       </c>
       <c r="F41">
-        <v>-0.09591521963247025</v>
+        <v>-0.09591521963246952</v>
       </c>
     </row>
     <row r="42">
@@ -1358,16 +1358,16 @@
         </is>
       </c>
       <c r="C42">
-        <v>0.6716875742703019</v>
+        <v>0.6716875742703021</v>
       </c>
       <c r="D42">
-        <v>0.7050830692851081</v>
+        <v>0.7050830692851083</v>
       </c>
       <c r="E42">
-        <v>0.189157253898606</v>
+        <v>0.1891572538986057</v>
       </c>
       <c r="F42">
-        <v>-0.02622708238531283</v>
+        <v>-0.02622708238531207</v>
       </c>
     </row>
     <row r="43">
@@ -1382,16 +1382,16 @@
         </is>
       </c>
       <c r="C43">
-        <v>-0.6877781766065717</v>
+        <v>-0.687778176606571</v>
       </c>
       <c r="D43">
-        <v>-0.3589106381966405</v>
+        <v>-0.35891063819664</v>
       </c>
       <c r="E43">
-        <v>-0.4359789046808175</v>
+        <v>-0.4359789046808166</v>
       </c>
       <c r="F43">
-        <v>-0.5714338677460843</v>
+        <v>-0.571433867746085</v>
       </c>
     </row>
     <row r="44">
@@ -1406,16 +1406,16 @@
         </is>
       </c>
       <c r="C44">
-        <v>0.6590784877710283</v>
+        <v>0.6590784877710278</v>
       </c>
       <c r="D44">
-        <v>-0.3487546003435557</v>
+        <v>-0.3487546003435554</v>
       </c>
       <c r="E44">
-        <v>-0.6757720946165852</v>
+        <v>-0.6757720946165853</v>
       </c>
       <c r="F44">
-        <v>-0.1245354131499981</v>
+        <v>-0.1245354131499972</v>
       </c>
     </row>
     <row r="45">
@@ -1430,16 +1430,16 @@
         </is>
       </c>
       <c r="C45">
-        <v>0.6198661414983664</v>
+        <v>0.6198661414983663</v>
       </c>
       <c r="D45">
-        <v>0.1066042848300443</v>
+        <v>0.1066042848300446</v>
       </c>
       <c r="E45">
-        <v>-0.2615982932361207</v>
+        <v>-0.2615982932361209</v>
       </c>
       <c r="F45">
-        <v>-0.05769905753115461</v>
+        <v>-0.05769905753115387</v>
       </c>
     </row>
     <row r="46">
@@ -1454,16 +1454,16 @@
         </is>
       </c>
       <c r="C46">
-        <v>-4.559522625893892</v>
+        <v>-4.559522625893891</v>
       </c>
       <c r="D46">
-        <v>0.3793309442012451</v>
+        <v>0.379330944201246</v>
       </c>
       <c r="E46">
-        <v>-1.15595467304138</v>
+        <v>-1.155954673041376</v>
       </c>
       <c r="F46">
-        <v>0.8493394531870961</v>
+        <v>0.8493394531870913</v>
       </c>
     </row>
     <row r="47">
@@ -1478,16 +1478,16 @@
         </is>
       </c>
       <c r="C47">
-        <v>0.6809416474282772</v>
+        <v>0.6809416474282771</v>
       </c>
       <c r="D47">
-        <v>0.09720687069670207</v>
+        <v>0.09720687069670235</v>
       </c>
       <c r="E47">
-        <v>-0.3065009622841396</v>
+        <v>-0.3065009622841399</v>
       </c>
       <c r="F47">
-        <v>-0.09989334171652094</v>
+        <v>-0.09989334171652009</v>
       </c>
     </row>
     <row r="48">
@@ -1502,16 +1502,16 @@
         </is>
       </c>
       <c r="C48">
-        <v>0.7118118746542138</v>
+        <v>0.7118118746542144</v>
       </c>
       <c r="D48">
         <v>1.354838339289548</v>
       </c>
       <c r="E48">
-        <v>0.7287728099034555</v>
+        <v>0.7287728099034549</v>
       </c>
       <c r="F48">
-        <v>0.001038135544285771</v>
+        <v>0.001038135544286556</v>
       </c>
     </row>
     <row r="49">
@@ -1526,16 +1526,16 @@
         </is>
       </c>
       <c r="C49">
-        <v>0.615313217439334</v>
+        <v>0.6153132174393335</v>
       </c>
       <c r="D49">
-        <v>-0.3359423217587689</v>
+        <v>-0.3359423217587684</v>
       </c>
       <c r="E49">
-        <v>-0.6133820693373713</v>
+        <v>-0.6133820693373714</v>
       </c>
       <c r="F49">
-        <v>-0.09702034701788571</v>
+        <v>-0.09702034701788492</v>
       </c>
     </row>
     <row r="50">
@@ -1550,16 +1550,16 @@
         </is>
       </c>
       <c r="C50">
-        <v>-0.5028756734860698</v>
+        <v>-0.5028756734860688</v>
       </c>
       <c r="D50">
-        <v>-0.03945143376097393</v>
+        <v>-0.0394514337609736</v>
       </c>
       <c r="E50">
-        <v>-0.7177435288543577</v>
+        <v>-0.7177435288543568</v>
       </c>
       <c r="F50">
-        <v>-0.8832070379118556</v>
+        <v>-0.8832070379118563</v>
       </c>
     </row>
     <row r="51">
@@ -1574,16 +1574,16 @@
         </is>
       </c>
       <c r="C51">
-        <v>0.6345167124608599</v>
+        <v>0.6345167124608595</v>
       </c>
       <c r="D51">
-        <v>-0.5431704017903877</v>
+        <v>-0.5431704017903874</v>
       </c>
       <c r="E51">
-        <v>-0.7687807682045815</v>
+        <v>-0.7687807682045816</v>
       </c>
       <c r="F51">
-        <v>-0.1418294853491626</v>
+        <v>-0.1418294853491618</v>
       </c>
     </row>
     <row r="52">
@@ -1598,16 +1598,16 @@
         </is>
       </c>
       <c r="C52">
-        <v>0.7038850069982724</v>
+        <v>0.7038850069982728</v>
       </c>
       <c r="D52">
         <v>1.291920052776503</v>
       </c>
       <c r="E52">
-        <v>0.6866790343001173</v>
+        <v>0.6866790343001166</v>
       </c>
       <c r="F52">
-        <v>-0.0007035974635003855</v>
+        <v>-0.0007035974634995723</v>
       </c>
     </row>
     <row r="53">
@@ -1622,16 +1622,16 @@
         </is>
       </c>
       <c r="C53">
-        <v>0.6652751726267169</v>
+        <v>0.6652751726267165</v>
       </c>
       <c r="D53">
-        <v>-0.2223555465407582</v>
+        <v>-0.2223555465407578</v>
       </c>
       <c r="E53">
-        <v>-0.5711094168865279</v>
+        <v>-0.5711094168865281</v>
       </c>
       <c r="F53">
-        <v>-0.117551100120294</v>
+        <v>-0.1175511001202932</v>
       </c>
     </row>
     <row r="54">
@@ -1646,16 +1646,16 @@
         </is>
       </c>
       <c r="C54">
-        <v>0.6561183045222067</v>
+        <v>0.6561183045222062</v>
       </c>
       <c r="D54">
-        <v>-0.4091359769098422</v>
+        <v>-0.4091359769098418</v>
       </c>
       <c r="E54">
-        <v>-0.7257699099982902</v>
+        <v>-0.7257699099982903</v>
       </c>
       <c r="F54">
-        <v>-0.1278718497958082</v>
+        <v>-0.1278718497958074</v>
       </c>
     </row>
     <row r="55">
@@ -1670,16 +1670,16 @@
         </is>
       </c>
       <c r="C55">
-        <v>0.6422546659099854</v>
+        <v>0.6422546659099851</v>
       </c>
       <c r="D55">
-        <v>-0.1901196710272894</v>
+        <v>-0.190119671027289</v>
       </c>
       <c r="E55">
-        <v>-0.4331623317677814</v>
+        <v>-0.4331623317677815</v>
       </c>
       <c r="F55">
-        <v>-0.1264927181793459</v>
+        <v>-0.1264927181793451</v>
       </c>
     </row>
     <row r="56">
@@ -1694,16 +1694,16 @@
         </is>
       </c>
       <c r="C56">
-        <v>0.851308682785032</v>
+        <v>0.851308682785034</v>
       </c>
       <c r="D56">
         <v>3.62917794832578</v>
       </c>
       <c r="E56">
-        <v>2.630694255934425</v>
+        <v>2.630694255934424</v>
       </c>
       <c r="F56">
-        <v>0.09405464920303026</v>
+        <v>0.09405464920303108</v>
       </c>
     </row>
     <row r="57">
@@ -1718,16 +1718,16 @@
         </is>
       </c>
       <c r="C57">
-        <v>0.6056717876223641</v>
+        <v>0.6056717876223637</v>
       </c>
       <c r="D57">
-        <v>-0.2314845879617271</v>
+        <v>-0.2314845879617267</v>
       </c>
       <c r="E57">
-        <v>-0.4181870553763757</v>
+        <v>-0.4181870553763758</v>
       </c>
       <c r="F57">
-        <v>-0.1106762189790973</v>
+        <v>-0.1106762189790965</v>
       </c>
     </row>
     <row r="58">
@@ -1742,16 +1742,16 @@
         </is>
       </c>
       <c r="C58">
-        <v>0.6047483614654512</v>
+        <v>0.6047483614654506</v>
       </c>
       <c r="D58">
-        <v>-0.7415221054233939</v>
+        <v>-0.7415221054233935</v>
       </c>
       <c r="E58">
         <v>-0.8423749620217393</v>
       </c>
       <c r="F58">
-        <v>-0.1615263397578783</v>
+        <v>-0.1615263397578776</v>
       </c>
     </row>
     <row r="59">
@@ -1766,16 +1766,16 @@
         </is>
       </c>
       <c r="C59">
-        <v>0.6667625117953909</v>
+        <v>0.6667625117953906</v>
       </c>
       <c r="D59">
-        <v>-0.1920170239302925</v>
+        <v>-0.1920170239302922</v>
       </c>
       <c r="E59">
-        <v>-0.5459880973888424</v>
+        <v>-0.5459880973888426</v>
       </c>
       <c r="F59">
-        <v>-0.1158747130557134</v>
+        <v>-0.1158747130557125</v>
       </c>
     </row>
     <row r="60">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="C60">
-        <v>0.6373173009207102</v>
+        <v>0.63731730092071</v>
       </c>
       <c r="D60">
-        <v>0.2112709818845664</v>
+        <v>0.2112709818845667</v>
       </c>
       <c r="E60">
-        <v>-0.212135732614562</v>
+        <v>-0.2121357326145622</v>
       </c>
       <c r="F60">
-        <v>-0.04957875603294563</v>
+        <v>-0.04957875603294487</v>
       </c>
     </row>
     <row r="61">
@@ -1814,16 +1814,16 @@
         </is>
       </c>
       <c r="C61">
-        <v>0.3755266439105387</v>
+        <v>0.3755266439105389</v>
       </c>
       <c r="D61">
-        <v>-0.4252599223836699</v>
+        <v>-0.4252599223836693</v>
       </c>
       <c r="E61">
-        <v>0.2246086571499256</v>
+        <v>0.2246086571499255</v>
       </c>
       <c r="F61">
-        <v>-0.1998932368923061</v>
+        <v>-0.1998932368923054</v>
       </c>
     </row>
     <row r="62">
@@ -1838,16 +1838,16 @@
         </is>
       </c>
       <c r="C62">
-        <v>0.6153569295609813</v>
+        <v>0.6153569295609809</v>
       </c>
       <c r="D62">
-        <v>-0.263483204019266</v>
+        <v>-0.2634832040192656</v>
       </c>
       <c r="E62">
-        <v>-0.5779886534410084</v>
+        <v>-0.5779886534410085</v>
       </c>
       <c r="F62">
-        <v>-0.08200696515426088</v>
+        <v>-0.08200696515426009</v>
       </c>
     </row>
     <row r="63">
@@ -1862,16 +1862,16 @@
         </is>
       </c>
       <c r="C63">
-        <v>0.6380713891141786</v>
+        <v>0.6380713891141782</v>
       </c>
       <c r="D63">
-        <v>-0.3020021366959148</v>
+        <v>-0.3020021366959145</v>
       </c>
       <c r="E63">
-        <v>-0.5990698763490515</v>
+        <v>-0.5990698763490517</v>
       </c>
       <c r="F63">
-        <v>-0.1112328658731385</v>
+        <v>-0.1112328658731377</v>
       </c>
     </row>
     <row r="64">
@@ -1886,16 +1886,16 @@
         </is>
       </c>
       <c r="C64">
-        <v>0.817290288305687</v>
+        <v>0.8172902883056887</v>
       </c>
       <c r="D64">
         <v>3.181480530296537</v>
       </c>
       <c r="E64">
-        <v>2.273436051203265</v>
+        <v>2.273436051203264</v>
       </c>
       <c r="F64">
-        <v>0.0767999373073409</v>
+        <v>0.07679993730734162</v>
       </c>
     </row>
     <row r="65">
@@ -1910,16 +1910,16 @@
         </is>
       </c>
       <c r="C65">
-        <v>0.575975342097313</v>
+        <v>0.5759753420973125</v>
       </c>
       <c r="D65">
-        <v>-0.577095940163077</v>
+        <v>-0.5770959401630765</v>
       </c>
       <c r="E65">
-        <v>-0.8018895314287771</v>
+        <v>-0.8018895314287772</v>
       </c>
       <c r="F65">
-        <v>-0.08724947803941098</v>
+        <v>-0.08724947803941019</v>
       </c>
     </row>
     <row r="66">
@@ -1934,16 +1934,16 @@
         </is>
       </c>
       <c r="C66">
-        <v>-0.4273279236270433</v>
+        <v>-0.4273279236270448</v>
       </c>
       <c r="D66">
-        <v>-0.06227619156850649</v>
+        <v>-0.06227619156850583</v>
       </c>
       <c r="E66">
-        <v>-0.3634819547733192</v>
+        <v>-0.3634819547733187</v>
       </c>
       <c r="F66">
-        <v>0.8787417112570726</v>
+        <v>0.8787417112570723</v>
       </c>
     </row>
     <row r="67">
@@ -1958,16 +1958,16 @@
         </is>
       </c>
       <c r="C67">
-        <v>0.643287491781081</v>
+        <v>0.6432874917810806</v>
       </c>
       <c r="D67">
-        <v>-0.3589822237200287</v>
+        <v>-0.3589822237200284</v>
       </c>
       <c r="E67">
-        <v>-0.6577006923694828</v>
+        <v>-0.6577006923694829</v>
       </c>
       <c r="F67">
-        <v>-0.1185651875050941</v>
+        <v>-0.1185651875050933</v>
       </c>
     </row>
     <row r="68">
@@ -1982,16 +1982,16 @@
         </is>
       </c>
       <c r="C68">
-        <v>-0.4133430074652237</v>
+        <v>-0.4133430074652252</v>
       </c>
       <c r="D68">
-        <v>-0.06696017617108491</v>
+        <v>-0.06696017617108417</v>
       </c>
       <c r="E68">
-        <v>-0.4323164002720326</v>
+        <v>-0.432316400272032</v>
       </c>
       <c r="F68">
-        <v>0.9363613919417735</v>
+        <v>0.9363613919417733</v>
       </c>
     </row>
     <row r="69">
@@ -2009,13 +2009,13 @@
         <v>0.4339342955081675</v>
       </c>
       <c r="D69">
-        <v>-0.1050941161165307</v>
+        <v>-0.1050941161165302</v>
       </c>
       <c r="E69">
-        <v>0.1179612226660149</v>
+        <v>0.1179612226660148</v>
       </c>
       <c r="F69">
-        <v>-0.07937029726767422</v>
+        <v>-0.0793702972676735</v>
       </c>
     </row>
     <row r="70">
@@ -2030,16 +2030,16 @@
         </is>
       </c>
       <c r="C70">
-        <v>0.6784248718396539</v>
+        <v>0.6784248718396537</v>
       </c>
       <c r="D70">
-        <v>0.04587005747407427</v>
+        <v>0.04587005747407456</v>
       </c>
       <c r="E70">
-        <v>-0.3490095743057995</v>
+        <v>-0.3490095743057997</v>
       </c>
       <c r="F70">
-        <v>-0.1027300114755658</v>
+        <v>-0.102730011475565</v>
       </c>
     </row>
     <row r="71">
@@ -2054,16 +2054,16 @@
         </is>
       </c>
       <c r="C71">
-        <v>0.6442093766016711</v>
+        <v>0.6442093766016709</v>
       </c>
       <c r="D71">
-        <v>-0.1894639681553461</v>
+        <v>-0.1894639681553457</v>
       </c>
       <c r="E71">
-        <v>-0.4413139761224064</v>
+        <v>-0.4413139761224065</v>
       </c>
       <c r="F71">
-        <v>-0.1256184929698881</v>
+        <v>-0.1256184929698874</v>
       </c>
     </row>
     <row r="72">
@@ -2078,16 +2078,16 @@
         </is>
       </c>
       <c r="C72">
-        <v>-4.384367646902826</v>
+        <v>-4.384367646902818</v>
       </c>
       <c r="D72">
         <v>2.20313834393265</v>
       </c>
       <c r="E72">
-        <v>-1.311141092522395</v>
+        <v>-1.31114109252239</v>
       </c>
       <c r="F72">
-        <v>-4.750193386088762</v>
+        <v>-4.750193386088768</v>
       </c>
     </row>
     <row r="73">
@@ -2105,13 +2105,13 @@
         <v>-2.297842187735997</v>
       </c>
       <c r="D73">
-        <v>0.4283325980499207</v>
+        <v>0.4283325980499211</v>
       </c>
       <c r="E73">
-        <v>-0.9452237371569804</v>
+        <v>-0.9452237371569783</v>
       </c>
       <c r="F73">
-        <v>-0.3579478007477643</v>
+        <v>-0.357947800747767</v>
       </c>
     </row>
     <row r="74">
@@ -2126,16 +2126,16 @@
         </is>
       </c>
       <c r="C74">
-        <v>0.4016543287728017</v>
+        <v>0.4016543287728022</v>
       </c>
       <c r="D74">
-        <v>-0.216599587484963</v>
+        <v>-0.2165995874849624</v>
       </c>
       <c r="E74">
-        <v>0.6271290831671464</v>
+        <v>0.627129083167146</v>
       </c>
       <c r="F74">
-        <v>-0.232261181615174</v>
+        <v>-0.2322611816151732</v>
       </c>
     </row>
     <row r="75">
@@ -2150,16 +2150,16 @@
         </is>
       </c>
       <c r="C75">
-        <v>-0.886676343887648</v>
+        <v>-0.886676343887649</v>
       </c>
       <c r="D75">
-        <v>-0.6675694084628786</v>
+        <v>-0.6675694084628776</v>
       </c>
       <c r="E75">
-        <v>-0.1972369602333224</v>
+        <v>-0.1972369602333215</v>
       </c>
       <c r="F75">
-        <v>0.6800572855730497</v>
+        <v>0.680057285573049</v>
       </c>
     </row>
     <row r="76">
@@ -2174,16 +2174,16 @@
         </is>
       </c>
       <c r="C76">
-        <v>-3.762663876607972</v>
+        <v>-3.762663876607975</v>
       </c>
       <c r="D76">
-        <v>0.386319924110716</v>
+        <v>0.3863199241107174</v>
       </c>
       <c r="E76">
-        <v>-0.8906976034679401</v>
+        <v>-0.890697603467937</v>
       </c>
       <c r="F76">
-        <v>3.212190371592868</v>
+        <v>3.212190371592864</v>
       </c>
     </row>
     <row r="77">
@@ -2198,16 +2198,16 @@
         </is>
       </c>
       <c r="C77">
-        <v>0.2282715934884853</v>
+        <v>0.2282715934884849</v>
       </c>
       <c r="D77">
-        <v>0.4026606414049423</v>
+        <v>0.4026606414049428</v>
       </c>
       <c r="E77">
-        <v>0.02527833198845594</v>
+        <v>0.02527833198845592</v>
       </c>
       <c r="F77">
-        <v>0.3439370488480026</v>
+        <v>0.343937048848003</v>
       </c>
     </row>
     <row r="78">
@@ -2222,16 +2222,16 @@
         </is>
       </c>
       <c r="C78">
-        <v>0.6515472273966976</v>
+        <v>0.6515472273966971</v>
       </c>
       <c r="D78">
-        <v>-0.3917006014054838</v>
+        <v>-0.3917006014054834</v>
       </c>
       <c r="E78">
-        <v>-0.6867950566141067</v>
+        <v>-0.6867950566141069</v>
       </c>
       <c r="F78">
-        <v>-0.1292734164837831</v>
+        <v>-0.1292734164837823</v>
       </c>
     </row>
     <row r="79">
@@ -2246,13 +2246,13 @@
         </is>
       </c>
       <c r="C79">
-        <v>-0.1632299682082315</v>
+        <v>-0.1632299682082327</v>
       </c>
       <c r="D79">
-        <v>-0.07525288918913056</v>
+        <v>-0.07525288918912997</v>
       </c>
       <c r="E79">
-        <v>-0.353554347794913</v>
+        <v>-0.3535543477949127</v>
       </c>
       <c r="F79">
         <v>0.6675667497263105</v>
@@ -2270,16 +2270,16 @@
         </is>
       </c>
       <c r="C80">
-        <v>0.6413267995019749</v>
+        <v>0.6413267995019748</v>
       </c>
       <c r="D80">
-        <v>0.008228754227621159</v>
+        <v>0.008228754227621524</v>
       </c>
       <c r="E80">
-        <v>-0.3266589255543291</v>
+        <v>-0.3266589255543292</v>
       </c>
       <c r="F80">
-        <v>-0.08736402964356756</v>
+        <v>-0.08736402964356677</v>
       </c>
     </row>
     <row r="81">
@@ -2297,10 +2297,10 @@
         <v>-0.3860587849707973</v>
       </c>
       <c r="D81">
-        <v>0.004295507749064491</v>
+        <v>0.004295507749065404</v>
       </c>
       <c r="E81">
-        <v>1.042758459978459</v>
+        <v>1.042758459978458</v>
       </c>
       <c r="F81">
         <v>0.3957748438660432</v>
@@ -2318,16 +2318,16 @@
         </is>
       </c>
       <c r="C82">
-        <v>0.1376067703316322</v>
+        <v>0.1376067703316314</v>
       </c>
       <c r="D82">
-        <v>-0.2416309197278288</v>
+        <v>-0.2416309197278282</v>
       </c>
       <c r="E82">
-        <v>-0.4648500998806145</v>
+        <v>-0.4648500998806143</v>
       </c>
       <c r="F82">
-        <v>0.3369902592510267</v>
+        <v>0.3369902592510269</v>
       </c>
     </row>
     <row r="83">
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="C83">
-        <v>-0.2440853588306727</v>
+        <v>-0.2440853588306739</v>
       </c>
       <c r="D83">
-        <v>-0.5208064235385347</v>
+        <v>-0.5208064235385339</v>
       </c>
       <c r="E83">
-        <v>-0.4363294279097772</v>
+        <v>-0.4363294279097767</v>
       </c>
       <c r="F83">
         <v>0.6010157506131736</v>
@@ -2366,16 +2366,16 @@
         </is>
       </c>
       <c r="C84">
-        <v>-1.803483256540634</v>
+        <v>-1.803483256540635</v>
       </c>
       <c r="D84">
-        <v>-1.499651385019499</v>
+        <v>-1.499651385019497</v>
       </c>
       <c r="E84">
-        <v>0.8183279442785022</v>
+        <v>0.8183279442785034</v>
       </c>
       <c r="F84">
-        <v>0.9684281288220286</v>
+        <v>0.9684281288220274</v>
       </c>
     </row>
     <row r="85">
@@ -2393,13 +2393,13 @@
         <v>0.6897394139195163</v>
       </c>
       <c r="D85">
-        <v>0.276662399897888</v>
+        <v>0.2766623998978883</v>
       </c>
       <c r="E85">
-        <v>-0.1579057342774179</v>
+        <v>-0.1579057342774181</v>
       </c>
       <c r="F85">
-        <v>-0.0899773371805397</v>
+        <v>-0.08997733718053885</v>
       </c>
     </row>
     <row r="86">
@@ -2414,16 +2414,16 @@
         </is>
       </c>
       <c r="C86">
-        <v>0.8335148839994705</v>
+        <v>0.8335148839994724</v>
       </c>
       <c r="D86">
         <v>3.344723547312227</v>
       </c>
       <c r="E86">
-        <v>2.386035334889983</v>
+        <v>2.386035334889982</v>
       </c>
       <c r="F86">
-        <v>0.08487730714433497</v>
+        <v>0.08487730714433579</v>
       </c>
     </row>
     <row r="87">
@@ -2441,13 +2441,13 @@
         <v>0.4836038999563199</v>
       </c>
       <c r="D87">
-        <v>-0.548682090514837</v>
+        <v>-0.5486820905148365</v>
       </c>
       <c r="E87">
-        <v>-0.0920800555179789</v>
+        <v>-0.09208005551797901</v>
       </c>
       <c r="F87">
-        <v>-0.2077950420269012</v>
+        <v>-0.2077950420269004</v>
       </c>
     </row>
     <row r="88">
@@ -2462,16 +2462,16 @@
         </is>
       </c>
       <c r="C88">
-        <v>0.5955153168445412</v>
+        <v>0.5955153168445406</v>
       </c>
       <c r="D88">
-        <v>-0.4707843310541447</v>
+        <v>-0.4707843310541444</v>
       </c>
       <c r="E88">
-        <v>-0.6901902460695397</v>
+        <v>-0.6901902460695398</v>
       </c>
       <c r="F88">
-        <v>-0.1025381018761442</v>
+        <v>-0.1025381018761435</v>
       </c>
     </row>
     <row r="89">
@@ -2486,16 +2486,16 @@
         </is>
       </c>
       <c r="C89">
-        <v>0.5684645636365848</v>
+        <v>0.5684645636365844</v>
       </c>
       <c r="D89">
-        <v>-0.2274511674303411</v>
+        <v>-0.2274511674303407</v>
       </c>
       <c r="E89">
-        <v>-0.5943263206148427</v>
+        <v>-0.5943263206148429</v>
       </c>
       <c r="F89">
-        <v>-0.018744172666442</v>
+        <v>-0.01874417266644124</v>
       </c>
     </row>
     <row r="90">
@@ -2513,13 +2513,13 @@
         <v>0.6967039405128437</v>
       </c>
       <c r="D90">
-        <v>0.4187237749850636</v>
+        <v>0.4187237749850639</v>
       </c>
       <c r="E90">
-        <v>-0.04027412651368339</v>
+        <v>-0.04027412651368369</v>
       </c>
       <c r="F90">
-        <v>-0.08212758606937216</v>
+        <v>-0.08212758606937132</v>
       </c>
     </row>
     <row r="91">
@@ -2534,16 +2534,16 @@
         </is>
       </c>
       <c r="C91">
-        <v>0.2524681449096247</v>
+        <v>0.2524681449096252</v>
       </c>
       <c r="D91">
-        <v>-0.7980062466861698</v>
+        <v>-0.7980062466861689</v>
       </c>
       <c r="E91">
-        <v>0.5848121011111584</v>
+        <v>0.5848121011111581</v>
       </c>
       <c r="F91">
-        <v>-0.304982792516596</v>
+        <v>-0.3049827925165952</v>
       </c>
     </row>
     <row r="92">
@@ -2558,16 +2558,16 @@
         </is>
       </c>
       <c r="C92">
-        <v>0.2336509630945797</v>
+        <v>0.23365096309458</v>
       </c>
       <c r="D92">
-        <v>-0.3554010615461383</v>
+        <v>-0.3554010615461376</v>
       </c>
       <c r="E92">
-        <v>0.5881822671209607</v>
+        <v>0.5881822671209604</v>
       </c>
       <c r="F92">
-        <v>-0.1078793166069402</v>
+        <v>-0.1078793166069396</v>
       </c>
     </row>
     <row r="93">
@@ -2582,16 +2582,16 @@
         </is>
       </c>
       <c r="C93">
-        <v>0.5395645480366276</v>
+        <v>0.5395645480366271</v>
       </c>
       <c r="D93">
-        <v>-0.304017619310174</v>
+        <v>-0.3040176193101735</v>
       </c>
       <c r="E93">
-        <v>-0.4610388557475254</v>
+        <v>-0.4610388557475255</v>
       </c>
       <c r="F93">
-        <v>-0.06868523440669339</v>
+        <v>-0.06868523440669258</v>
       </c>
     </row>
     <row r="94">
@@ -2606,16 +2606,16 @@
         </is>
       </c>
       <c r="C94">
-        <v>0.6374564043376283</v>
+        <v>0.6374564043376282</v>
       </c>
       <c r="D94">
-        <v>0.2804674524059717</v>
+        <v>0.280467452405972</v>
       </c>
       <c r="E94">
-        <v>-0.1650779834541419</v>
+        <v>-0.1650779834541421</v>
       </c>
       <c r="F94">
-        <v>-0.03592402615574273</v>
+        <v>-0.03592402615574197</v>
       </c>
     </row>
     <row r="95">
@@ -2630,16 +2630,16 @@
         </is>
       </c>
       <c r="C95">
-        <v>-1.157356301758223</v>
+        <v>-1.157356301758224</v>
       </c>
       <c r="D95">
         <v>-1.147910617561533</v>
       </c>
       <c r="E95">
-        <v>0.5719444246043999</v>
+        <v>0.5719444246044006</v>
       </c>
       <c r="F95">
-        <v>0.5468197389099323</v>
+        <v>0.5468197389099317</v>
       </c>
     </row>
     <row r="96">
@@ -2654,16 +2654,16 @@
         </is>
       </c>
       <c r="C96">
-        <v>-0.6681094195816574</v>
+        <v>-0.6681094195816557</v>
       </c>
       <c r="D96">
-        <v>-2.292936234272004</v>
+        <v>-2.292936234272002</v>
       </c>
       <c r="E96">
-        <v>2.633372104184302</v>
+        <v>2.633372104184301</v>
       </c>
       <c r="F96">
-        <v>-0.5745516969129018</v>
+        <v>-0.5745516969129011</v>
       </c>
     </row>
     <row r="97">
@@ -2678,16 +2678,16 @@
         </is>
       </c>
       <c r="C97">
-        <v>0.653125100234788</v>
+        <v>0.6531251002347875</v>
       </c>
       <c r="D97">
-        <v>-0.4701909116982206</v>
+        <v>-0.4701909116982202</v>
       </c>
       <c r="E97">
         <v>-0.7763254542949697</v>
       </c>
       <c r="F97">
-        <v>-0.1312455046115752</v>
+        <v>-0.1312455046115744</v>
       </c>
     </row>
     <row r="98">
@@ -2705,13 +2705,13 @@
         <v>-1.326444619692954</v>
       </c>
       <c r="D98">
-        <v>-1.191791033272636</v>
+        <v>-1.191791033272635</v>
       </c>
       <c r="E98">
-        <v>0.3882428001475736</v>
+        <v>0.3882428001475747</v>
       </c>
       <c r="F98">
-        <v>-0.2433735607691455</v>
+        <v>-0.2433735607691463</v>
       </c>
     </row>
     <row r="99">
@@ -2726,16 +2726,16 @@
         </is>
       </c>
       <c r="C99">
-        <v>0.3964259497704039</v>
+        <v>0.3964259497704037</v>
       </c>
       <c r="D99">
-        <v>-0.7740359847009122</v>
+        <v>-0.7740359847009116</v>
       </c>
       <c r="E99">
-        <v>-0.1101261092850109</v>
+        <v>-0.110126109285011</v>
       </c>
       <c r="F99">
-        <v>-0.1989851367001557</v>
+        <v>-0.1989851367001548</v>
       </c>
     </row>
     <row r="100">
@@ -2750,16 +2750,16 @@
         </is>
       </c>
       <c r="C100">
-        <v>0.5667425454796026</v>
+        <v>0.5667425454796022</v>
       </c>
       <c r="D100">
-        <v>-0.2304905698749621</v>
+        <v>-0.2304905698749618</v>
       </c>
       <c r="E100">
-        <v>-0.3134192786187514</v>
+        <v>-0.3134192786187515</v>
       </c>
       <c r="F100">
-        <v>-0.109648118172702</v>
+        <v>-0.1096481181727012</v>
       </c>
     </row>
     <row r="101">
@@ -2774,16 +2774,16 @@
         </is>
       </c>
       <c r="C101">
-        <v>0.6588901641835353</v>
+        <v>0.6588901641835349</v>
       </c>
       <c r="D101">
-        <v>-0.3525959968034723</v>
+        <v>-0.3525959968034719</v>
       </c>
       <c r="E101">
-        <v>-0.6789529003870531</v>
+        <v>-0.6789529003870532</v>
       </c>
       <c r="F101">
-        <v>-0.1247476735628736</v>
+        <v>-0.1247476735628728</v>
       </c>
     </row>
     <row r="102">
@@ -2798,16 +2798,16 @@
         </is>
       </c>
       <c r="C102">
-        <v>0.6212465037926568</v>
+        <v>0.6212465037926563</v>
       </c>
       <c r="D102">
-        <v>-0.4393446614287128</v>
+        <v>-0.4393446614287124</v>
       </c>
       <c r="E102">
-        <v>-0.739828710503083</v>
+        <v>-0.7398287105030831</v>
       </c>
       <c r="F102">
-        <v>-0.1007054444052518</v>
+        <v>-0.1007054444052509</v>
       </c>
     </row>
     <row r="103">
@@ -2822,16 +2822,16 @@
         </is>
       </c>
       <c r="C103">
-        <v>0.6472712590386481</v>
+        <v>0.6472712590386477</v>
       </c>
       <c r="D103">
-        <v>-0.3491682149887632</v>
+        <v>-0.3491682149887629</v>
       </c>
       <c r="E103">
         <v>-0.647520620938957</v>
       </c>
       <c r="F103">
-        <v>-0.1220400103829725</v>
+        <v>-0.1220400103829717</v>
       </c>
     </row>
     <row r="104">
@@ -2846,16 +2846,16 @@
         </is>
       </c>
       <c r="C104">
-        <v>0.6136443184860285</v>
+        <v>0.6136443184860281</v>
       </c>
       <c r="D104">
-        <v>-0.3088431142169508</v>
+        <v>-0.3088431142169505</v>
       </c>
       <c r="E104">
-        <v>-0.6520478002601091</v>
+        <v>-0.6520478002601093</v>
       </c>
       <c r="F104">
-        <v>-0.07369868074767801</v>
+        <v>-0.07369868074767716</v>
       </c>
     </row>
     <row r="105">
@@ -2870,16 +2870,16 @@
         </is>
       </c>
       <c r="C105">
-        <v>0.651845178485321</v>
+        <v>0.6518451784853205</v>
       </c>
       <c r="D105">
-        <v>-0.4962985647162262</v>
+        <v>-0.4962985647162256</v>
       </c>
       <c r="E105">
-        <v>-0.7979434711384724</v>
+        <v>-0.7979434711384722</v>
       </c>
       <c r="F105">
-        <v>-0.1326881105145682</v>
+        <v>-0.1326881105145674</v>
       </c>
     </row>
     <row r="106">
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C106">
-        <v>-3.448001640281439</v>
+        <v>-3.448001640281438</v>
       </c>
       <c r="D106">
-        <v>-2.371823769249277</v>
+        <v>-2.371823769249274</v>
       </c>
       <c r="E106">
-        <v>1.911700914266653</v>
+        <v>1.911700914266655</v>
       </c>
       <c r="F106">
-        <v>0.6162396039807744</v>
+        <v>0.6162396039807717</v>
       </c>
     </row>
     <row r="107">
@@ -2918,16 +2918,16 @@
         </is>
       </c>
       <c r="C107">
-        <v>0.4233919337924481</v>
+        <v>0.4233919337924477</v>
       </c>
       <c r="D107">
-        <v>-0.5844617701942075</v>
+        <v>-0.5844617701942071</v>
       </c>
       <c r="E107">
-        <v>-0.49248792874149</v>
+        <v>-0.4924879287414899</v>
       </c>
       <c r="F107">
-        <v>-0.03847421693438225</v>
+        <v>-0.03847421693438161</v>
       </c>
     </row>
     <row r="108">
@@ -2942,16 +2942,16 @@
         </is>
       </c>
       <c r="C108">
-        <v>0.5722752339537022</v>
+        <v>0.5722752339537018</v>
       </c>
       <c r="D108">
-        <v>-0.4255823269931234</v>
+        <v>-0.4255823269931229</v>
       </c>
       <c r="E108">
-        <v>-0.5226716210820687</v>
+        <v>-0.5226716210820689</v>
       </c>
       <c r="F108">
-        <v>-0.1321102512743088</v>
+        <v>-0.1321102512743081</v>
       </c>
     </row>
     <row r="109">
@@ -2966,16 +2966,16 @@
         </is>
       </c>
       <c r="C109">
-        <v>0.6391771604252242</v>
+        <v>0.6391771604252239</v>
       </c>
       <c r="D109">
-        <v>-0.2612164654703297</v>
+        <v>-0.2612164654703294</v>
       </c>
       <c r="E109">
-        <v>-0.5505992095902256</v>
+        <v>-0.5505992095902258</v>
       </c>
       <c r="F109">
-        <v>-0.1126704249317818</v>
+        <v>-0.112670424931781</v>
       </c>
     </row>
     <row r="110">
@@ -2993,13 +2993,13 @@
         <v>-1.324522702134487</v>
       </c>
       <c r="D110">
-        <v>-1.170508713930182</v>
+        <v>-1.170508713930181</v>
       </c>
       <c r="E110">
-        <v>0.4217797273217254</v>
+        <v>0.4217797273217265</v>
       </c>
       <c r="F110">
-        <v>0.05222305523894243</v>
+        <v>0.0522230552389415</v>
       </c>
     </row>
     <row r="111">
@@ -3017,13 +3017,13 @@
         <v>0.583376058660892</v>
       </c>
       <c r="D111">
-        <v>0.4268622281690063</v>
+        <v>0.4268622281690066</v>
       </c>
       <c r="E111">
-        <v>0.03419609166679943</v>
+        <v>0.03419609166679911</v>
       </c>
       <c r="F111">
-        <v>0.007109948139915492</v>
+        <v>0.007109948139916167</v>
       </c>
     </row>
     <row r="112">
@@ -3038,16 +3038,16 @@
         </is>
       </c>
       <c r="C112">
-        <v>0.6491233908723144</v>
+        <v>0.6491233908723145</v>
       </c>
       <c r="D112">
-        <v>0.5534571517751363</v>
+        <v>0.5534571517751367</v>
       </c>
       <c r="E112">
-        <v>0.06062902814234708</v>
+        <v>0.06062902814234684</v>
       </c>
       <c r="F112">
-        <v>-0.01907849380119873</v>
+        <v>-0.01907849380119797</v>
       </c>
     </row>
     <row r="113">
@@ -3062,16 +3062,16 @@
         </is>
       </c>
       <c r="C113">
-        <v>0.6735586984884067</v>
+        <v>0.6735586984884069</v>
       </c>
       <c r="D113">
-        <v>0.7387099010957392</v>
+        <v>0.7387099010957393</v>
       </c>
       <c r="E113">
-        <v>0.2170451943886214</v>
+        <v>0.217045194388621</v>
       </c>
       <c r="F113">
-        <v>-0.02459739920097585</v>
+        <v>-0.02459739920097503</v>
       </c>
     </row>
     <row r="114">
@@ -3086,16 +3086,16 @@
         </is>
       </c>
       <c r="C114">
-        <v>-0.8197096002976769</v>
+        <v>-0.8197096002976778</v>
       </c>
       <c r="D114">
-        <v>0.07373101196807598</v>
+        <v>0.0737310119680767</v>
       </c>
       <c r="E114">
-        <v>-0.1565139485995509</v>
+        <v>-0.1565139485995501</v>
       </c>
       <c r="F114">
-        <v>0.7871214240603249</v>
+        <v>0.7871214240603243</v>
       </c>
     </row>
     <row r="115">
@@ -3110,16 +3110,16 @@
         </is>
       </c>
       <c r="C115">
-        <v>-1.173006897904046</v>
+        <v>-1.173006897904048</v>
       </c>
       <c r="D115">
-        <v>0.5232867673883149</v>
+        <v>0.5232867673883158</v>
       </c>
       <c r="E115">
-        <v>-0.3295301412299123</v>
+        <v>-0.3295301412299113</v>
       </c>
       <c r="F115">
-        <v>1.813357228771156</v>
+        <v>1.813357228771155</v>
       </c>
     </row>
     <row r="116">
@@ -3134,13 +3134,13 @@
         </is>
       </c>
       <c r="C116">
-        <v>0.04013128788301853</v>
+        <v>0.0401312878830194</v>
       </c>
       <c r="D116">
-        <v>0.1399250357922744</v>
+        <v>0.1399250357922747</v>
       </c>
       <c r="E116">
-        <v>-0.3729403745889289</v>
+        <v>-0.3729403745889286</v>
       </c>
       <c r="F116">
         <v>-0.7300700805089211</v>
@@ -3158,16 +3158,16 @@
         </is>
       </c>
       <c r="C117">
-        <v>-1.692544607258671</v>
+        <v>-1.692544607258669</v>
       </c>
       <c r="D117">
-        <v>-4.069980892146762</v>
+        <v>-4.069980892146759</v>
       </c>
       <c r="E117">
-        <v>4.390601228880672</v>
+        <v>4.390601228880673</v>
       </c>
       <c r="F117">
-        <v>-0.9905209629980071</v>
+        <v>-0.9905209629980066</v>
       </c>
     </row>
     <row r="118">
@@ -3182,16 +3182,16 @@
         </is>
       </c>
       <c r="C118">
-        <v>0.6631313629442053</v>
+        <v>0.6631313629442048</v>
       </c>
       <c r="D118">
-        <v>-0.2660846568171969</v>
+        <v>-0.2660846568171966</v>
       </c>
       <c r="E118">
-        <v>-0.6073185943968721</v>
+        <v>-0.6073185943968723</v>
       </c>
       <c r="F118">
-        <v>-0.1199673982292783</v>
+        <v>-0.1199673982292774</v>
       </c>
     </row>
     <row r="119">
@@ -3206,16 +3206,16 @@
         </is>
       </c>
       <c r="C119">
-        <v>-0.211065984029426</v>
+        <v>-0.2110659840294261</v>
       </c>
       <c r="D119">
         <v>-1.001181127503781</v>
       </c>
       <c r="E119">
-        <v>0.5552602340732502</v>
+        <v>0.5552602340732505</v>
       </c>
       <c r="F119">
-        <v>0.02635234298077971</v>
+        <v>0.02635234298078004</v>
       </c>
     </row>
     <row r="120">
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="C120">
-        <v>0.5898377774576448</v>
+        <v>0.5898377774576444</v>
       </c>
       <c r="D120">
-        <v>-0.05989636475150739</v>
+        <v>-0.05989636475150707</v>
       </c>
       <c r="E120">
-        <v>-0.452996392334629</v>
+        <v>-0.4529963923346291</v>
       </c>
       <c r="F120">
-        <v>-0.02298909601127511</v>
+        <v>-0.02298909601127436</v>
       </c>
     </row>
     <row r="121">
@@ -3254,16 +3254,16 @@
         </is>
       </c>
       <c r="C121">
-        <v>-6.990577146071927</v>
+        <v>-6.990577146071922</v>
       </c>
       <c r="D121">
         <v>3.083173495115317</v>
       </c>
       <c r="E121">
-        <v>-1.277819203534816</v>
+        <v>-1.27781920353481</v>
       </c>
       <c r="F121">
-        <v>-1.253673892536375</v>
+        <v>-1.253673892536384</v>
       </c>
     </row>
     <row r="122">
@@ -3278,16 +3278,16 @@
         </is>
       </c>
       <c r="C122">
-        <v>-0.02367172123477383</v>
+        <v>-0.02367172123477462</v>
       </c>
       <c r="D122">
-        <v>0.0803571658677686</v>
+        <v>0.08035716586776913</v>
       </c>
       <c r="E122">
-        <v>-0.2163598053984156</v>
+        <v>-0.2163598053984153</v>
       </c>
       <c r="F122">
-        <v>0.5060386371039647</v>
+        <v>0.5060386371039648</v>
       </c>
     </row>
     <row r="123">
@@ -3302,7 +3302,7 @@
         </is>
       </c>
       <c r="C123">
-        <v>0.6721879649889584</v>
+        <v>0.6721879649889592</v>
       </c>
       <c r="D123">
         <v>1.374792237152767</v>
@@ -3311,7 +3311,7 @@
         <v>1.074222699032551</v>
       </c>
       <c r="F123">
-        <v>-0.06041466757307402</v>
+        <v>-0.06041466757307323</v>
       </c>
     </row>
     <row r="124">
@@ -3326,16 +3326,16 @@
         </is>
       </c>
       <c r="C124">
-        <v>0.4416438618756083</v>
+        <v>0.4416438618756096</v>
       </c>
       <c r="D124">
         <v>2.846972118612528</v>
       </c>
       <c r="E124">
-        <v>2.00213633800604</v>
+        <v>2.002136338006039</v>
       </c>
       <c r="F124">
-        <v>0.3837703083966686</v>
+        <v>0.3837703083966691</v>
       </c>
     </row>
     <row r="125">
@@ -3350,16 +3350,16 @@
         </is>
       </c>
       <c r="C125">
-        <v>-0.2785410149535712</v>
+        <v>-0.2785410149535728</v>
       </c>
       <c r="D125">
-        <v>-0.1803906829229609</v>
+        <v>-0.1803906829229601</v>
       </c>
       <c r="E125">
-        <v>-0.713029403663884</v>
+        <v>-0.7130294036638835</v>
       </c>
       <c r="F125">
-        <v>0.7651723361906924</v>
+        <v>0.7651723361906921</v>
       </c>
     </row>
     <row r="126">
@@ -3377,13 +3377,13 @@
         <v>-4.062591112592307</v>
       </c>
       <c r="D126">
-        <v>0.4427678537487771</v>
+        <v>0.442767853748778</v>
       </c>
       <c r="E126">
-        <v>-0.9422918728710376</v>
+        <v>-0.942291872871034</v>
       </c>
       <c r="F126">
-        <v>0.1709976623358207</v>
+        <v>0.170997662335816</v>
       </c>
     </row>
   </sheetData>
